--- a/2310Signal.xlsx
+++ b/2310Signal.xlsx
@@ -17,11 +17,11 @@
   <calcPr calcOnSave="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1740840553" val="982" rev="124" rev64="64" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1740840553" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1740840553" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1740840553"/>
-      <pm:sortOptions xmlns:pm="smNativeData" id="1740840553" headings="1">
+      <pm:revision xmlns:pm="smNativeData" day="1785693389" val="982" rev="124" rev64="64" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1785693389" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1785693389" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1785693389"/>
+      <pm:sortOptions xmlns:pm="smNativeData" id="1785693389" headings="1">
         <pm:column colId="8"/>
         <pm:column colId="-1"/>
         <pm:column colId="-1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="268">
   <si>
     <t>By FPGA pin</t>
   </si>
@@ -678,6 +678,213 @@
   </si>
   <si>
     <t>By cable</t>
+  </si>
+  <si>
+    <t>Terminator resistors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179 ohm </t>
+  </si>
+  <si>
+    <t>249 ohm</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R53</t>
+  </si>
+  <si>
+    <t>R54</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>R51</t>
+  </si>
+  <si>
+    <t>R52</t>
+  </si>
+  <si>
+    <t>R47</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>R39</t>
+  </si>
+  <si>
+    <t>R40</t>
+  </si>
+  <si>
+    <t>R41</t>
+  </si>
+  <si>
+    <t>R42</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t>R35</t>
+  </si>
+  <si>
+    <t>R36</t>
+  </si>
+  <si>
+    <t>R58</t>
+  </si>
+  <si>
+    <t>R59</t>
+  </si>
+  <si>
+    <t>R70</t>
+  </si>
+  <si>
+    <t>R69</t>
+  </si>
+  <si>
+    <t>R60</t>
+  </si>
+  <si>
+    <t>R61</t>
+  </si>
+  <si>
+    <t>R62</t>
+  </si>
+  <si>
+    <t>R63</t>
+  </si>
+  <si>
+    <t>R74</t>
+  </si>
+  <si>
+    <t>R73</t>
+  </si>
+  <si>
+    <t>R64</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>R108</t>
+  </si>
+  <si>
+    <t>R107</t>
+  </si>
+  <si>
+    <t>R66</t>
+  </si>
+  <si>
+    <t>R67</t>
+  </si>
+  <si>
+    <t>R106</t>
+  </si>
+  <si>
+    <t>R105</t>
+  </si>
+  <si>
+    <t>R110</t>
+  </si>
+  <si>
+    <t>R109</t>
+  </si>
+  <si>
+    <t>R104</t>
+  </si>
+  <si>
+    <t>R103</t>
+  </si>
+  <si>
+    <t>R86</t>
+  </si>
+  <si>
+    <t>R85</t>
+  </si>
+  <si>
+    <t>R84</t>
+  </si>
+  <si>
+    <t>R83</t>
+  </si>
+  <si>
+    <t>R88</t>
+  </si>
+  <si>
+    <t>R87</t>
+  </si>
+  <si>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>R89</t>
+  </si>
+  <si>
+    <t>R94</t>
+  </si>
+  <si>
+    <t>R93</t>
   </si>
   <si>
     <t>Special version for archiving</t>
@@ -715,7 +922,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1740840553" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785693389" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -731,7 +938,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1740840553" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785693389" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -747,7 +954,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1740840553" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785693389" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -756,7 +963,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -769,7 +976,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1740840553" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785693389" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -780,7 +987,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1740840553" type="1" fgLvl="64" fgClr="0000FFFF" bgLvl="36" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785693389" type="1" fgLvl="64" fgClr="0000FFFF" bgLvl="36" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -791,13 +998,24 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1740840553" type="1" fgLvl="76" fgClr="0000FF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785693389" type="1" fgLvl="76" fgClr="0000FF00" bgLvl="24" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785693389" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -813,7 +1031,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1740840553"/>
+          <pm:border xmlns:pm="smNativeData" id="1785693389"/>
         </ext>
       </extLst>
     </border>
@@ -832,7 +1050,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1740840553"/>
+          <pm:border xmlns:pm="smNativeData" id="1785693389"/>
         </ext>
       </extLst>
     </border>
@@ -851,7 +1069,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1740840553"/>
+          <pm:border xmlns:pm="smNativeData" id="1785693389"/>
         </ext>
       </extLst>
     </border>
@@ -870,7 +1088,26 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1740840553"/>
+          <pm:border xmlns:pm="smNativeData" id="1785693389"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785693389"/>
         </ext>
       </extLst>
     </border>
@@ -878,7 +1115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -919,6 +1156,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -926,10 +1170,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1740840553" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1785693389" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1740840553" count="27">
+      <pm:colors xmlns:pm="smNativeData" id="1785693389" count="27">
         <pm:color name="Color 24" rgb="FFFF9E"/>
         <pm:color name="Color 25" rgb="010180"/>
         <pm:color name="Color 26" rgb="0000A3"/>
@@ -1219,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P266"/>
+  <dimension ref="A1:U266"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="27.162162" customWidth="1" style="2"/>
@@ -5179,12 +5423,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="131" spans="9:9">
+    <row r="131" spans="9:17">
       <c r="I131" s="13" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="132" spans="8:16">
+      <c r="Q131" s="16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="132" spans="8:18">
       <c r="H132" s="4" t="s">
         <v>8</v>
       </c>
@@ -5212,8 +5459,14 @@
       <c r="P132" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="133" spans="8:15">
+      <c r="Q132" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="R132" s="17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="133" spans="8:18">
       <c r="H133" s="5" t="n">
         <v>121</v>
       </c>
@@ -5238,8 +5491,14 @@
       <c r="O133" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="134" spans="8:15">
+      <c r="Q133" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="R133" s="18" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="134" spans="8:18">
       <c r="H134" s="5" t="n">
         <v>122</v>
       </c>
@@ -5264,8 +5523,14 @@
       <c r="O134" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="135" spans="8:15">
+      <c r="Q134" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="R134" s="18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="135" spans="8:18">
       <c r="H135" s="5" t="n">
         <v>128</v>
       </c>
@@ -5290,8 +5555,14 @@
       <c r="O135" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="136" spans="8:15">
+      <c r="Q135" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="R135" s="18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="136" spans="8:21">
       <c r="H136" s="5" t="n">
         <v>129</v>
       </c>
@@ -5316,8 +5587,15 @@
       <c r="O136" s="6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="137" spans="8:16">
+      <c r="Q136" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="R136" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="U136"/>
+    </row>
+    <row r="137" spans="8:18">
       <c r="H137" s="5" t="n">
         <v>99</v>
       </c>
@@ -5342,8 +5620,14 @@
       <c r="P137" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="138" spans="8:15">
+      <c r="Q137" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="R137" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="138" spans="8:18">
       <c r="H138" s="5" t="n">
         <v>134</v>
       </c>
@@ -5368,8 +5652,14 @@
       <c r="O138" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="139" spans="8:16">
+      <c r="Q138" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="R138" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="139" spans="8:18">
       <c r="H139" s="5" t="n">
         <v>107</v>
       </c>
@@ -5394,8 +5684,14 @@
       <c r="P139" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="140" spans="8:15">
+      <c r="Q139" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="R139" s="18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="140" spans="8:18">
       <c r="H140" s="5" t="n">
         <v>135</v>
       </c>
@@ -5420,8 +5716,14 @@
       <c r="O140" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="141" spans="8:14">
+      <c r="Q140" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="R140" s="18" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="141" spans="8:18">
       <c r="H141" s="5" t="n">
         <v>101</v>
       </c>
@@ -5443,8 +5745,10 @@
       <c r="N141" s="5" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="142" spans="8:15">
+      <c r="Q141" s="18"/>
+      <c r="R141" s="18"/>
+    </row>
+    <row r="142" spans="8:18">
       <c r="H142" s="5" t="n">
         <v>136</v>
       </c>
@@ -5469,8 +5773,14 @@
       <c r="O142" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="143" spans="8:15">
+      <c r="Q142" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="R142" s="18" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="143" spans="8:18">
       <c r="H143" s="5" t="n">
         <v>102</v>
       </c>
@@ -5495,8 +5805,14 @@
       <c r="O143" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="144" spans="8:14">
+      <c r="Q143" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="R143" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="144" spans="8:18">
       <c r="H144" s="5" t="n">
         <v>137</v>
       </c>
@@ -5518,8 +5834,10 @@
       <c r="N144" s="5" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="145" spans="8:15">
+      <c r="Q144" s="18"/>
+      <c r="R144" s="18"/>
+    </row>
+    <row r="145" spans="8:18">
       <c r="H145" s="5" t="n">
         <v>104</v>
       </c>
@@ -5544,8 +5862,14 @@
       <c r="O145" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="146" spans="8:16">
+      <c r="Q145" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="R145" s="18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="146" spans="8:18">
       <c r="H146" s="5" t="n">
         <v>97</v>
       </c>
@@ -5570,8 +5894,14 @@
       <c r="P146" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="147" spans="8:15">
+      <c r="Q146" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="R146" s="18" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="147" spans="8:18">
       <c r="H147" s="5" t="n">
         <v>105</v>
       </c>
@@ -5596,8 +5926,14 @@
       <c r="O147" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="148" spans="8:15">
+      <c r="Q147" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="R147" s="18" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="148" spans="8:18">
       <c r="H148" s="5" t="n">
         <v>52</v>
       </c>
@@ -5622,8 +5958,14 @@
       <c r="O148" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="149" spans="8:16">
+      <c r="Q148" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="R148" s="18" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="149" spans="8:18">
       <c r="H149" s="5" t="n">
         <v>106</v>
       </c>
@@ -5648,8 +5990,14 @@
       <c r="P149" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="150" spans="8:16">
+      <c r="Q149" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="R149" s="18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="150" spans="8:18">
       <c r="H150" s="5" t="n">
         <v>96</v>
       </c>
@@ -5674,8 +6022,14 @@
       <c r="P150" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="151" spans="8:16">
+      <c r="Q150" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="R150" s="18" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="151" spans="8:18">
       <c r="H151" s="5" t="n">
         <v>95</v>
       </c>
@@ -5700,8 +6054,14 @@
       <c r="P151" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="152" spans="8:16">
+      <c r="Q151" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="R151" s="18" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="152" spans="8:18">
       <c r="H152" s="5" t="n">
         <v>98</v>
       </c>
@@ -5726,8 +6086,14 @@
       <c r="P152" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="153" spans="8:14">
+      <c r="Q152" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="R152" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="153" spans="8:18">
       <c r="H153"/>
       <c r="I153" s="6" t="s">
         <v>189</v>
@@ -5745,8 +6111,10 @@
       <c r="N153" s="5" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="8:15">
+      <c r="Q153" s="18"/>
+      <c r="R153" s="18"/>
+    </row>
+    <row r="154" spans="8:18">
       <c r="H154" s="5" t="s">
         <v>187</v>
       </c>
@@ -5767,8 +6135,10 @@
         <v>3</v>
       </c>
       <c r="O154"/>
-    </row>
-    <row r="155" spans="8:16">
+      <c r="Q154" s="18"/>
+      <c r="R154" s="18"/>
+    </row>
+    <row r="155" spans="8:18">
       <c r="H155" s="5" t="n">
         <v>88</v>
       </c>
@@ -5793,8 +6163,14 @@
       <c r="P155" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="156" spans="8:15">
+      <c r="Q155" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="R155" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="156" spans="8:18">
       <c r="H156" s="5" t="n">
         <v>87</v>
       </c>
@@ -5819,8 +6195,14 @@
       <c r="O156" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="157" spans="8:15">
+      <c r="Q156" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="R156" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="157" spans="8:18">
       <c r="H157" s="5" t="n">
         <v>81</v>
       </c>
@@ -5845,8 +6227,14 @@
       <c r="O157" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="158" spans="8:16">
+      <c r="Q157" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="R157" s="18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="158" spans="8:18">
       <c r="H158" s="5" t="n">
         <v>80</v>
       </c>
@@ -5871,8 +6259,14 @@
       <c r="P158" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="159" spans="8:15">
+      <c r="Q158" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="R158" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="159" spans="8:18">
       <c r="H159" s="5" t="n">
         <v>63</v>
       </c>
@@ -5897,8 +6291,14 @@
       <c r="O159" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="160" spans="8:15">
+      <c r="Q159" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="R159" s="18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="160" spans="8:18">
       <c r="H160" s="5" t="n">
         <v>79</v>
       </c>
@@ -5923,8 +6323,14 @@
       <c r="O160" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="161" spans="8:16">
+      <c r="Q160" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="R160" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="161" spans="8:18">
       <c r="H161" s="5" t="n">
         <v>91</v>
       </c>
@@ -5949,8 +6355,14 @@
       <c r="P161" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="162" spans="8:16">
+      <c r="Q161" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="R161" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="162" spans="8:18">
       <c r="H162" s="5" t="n">
         <v>78</v>
       </c>
@@ -5975,8 +6387,14 @@
       <c r="P162" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="163" spans="8:16">
+      <c r="Q162" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="R162" s="18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="163" spans="8:18">
       <c r="H163" s="5" t="n">
         <v>93</v>
       </c>
@@ -6001,8 +6419,14 @@
       <c r="P163" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="164" spans="8:16">
+      <c r="Q163" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="R163" s="18" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="164" spans="8:18">
       <c r="H164" s="5" t="n">
         <v>62</v>
       </c>
@@ -6027,8 +6451,14 @@
       <c r="P164" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="165" spans="8:16">
+      <c r="Q164" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="R164" s="18" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="165" spans="8:18">
       <c r="H165" s="5" t="n">
         <v>64</v>
       </c>
@@ -6053,8 +6483,14 @@
       <c r="P165" s="6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="166" spans="8:15">
+      <c r="Q165" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="R165" s="18" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="166" spans="8:18">
       <c r="H166" s="5" t="n">
         <v>61</v>
       </c>
@@ -6079,8 +6515,14 @@
       <c r="O166" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="167" spans="8:15">
+      <c r="Q166" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="R166" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="167" spans="8:18">
       <c r="H167" s="5" t="n">
         <v>60</v>
       </c>
@@ -6105,8 +6547,14 @@
       <c r="O167" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="168" spans="8:16">
+      <c r="Q167" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="R167" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="168" spans="8:18">
       <c r="H168" s="5" t="n">
         <v>90</v>
       </c>
@@ -6131,8 +6579,14 @@
       <c r="P168" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="169" spans="8:14">
+      <c r="Q168" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="R168" s="18" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="169" spans="8:18">
       <c r="H169" s="5" t="n">
         <v>94</v>
       </c>
@@ -6152,8 +6606,10 @@
       <c r="N169" s="5" t="n">
         <v>33</v>
       </c>
-    </row>
-    <row r="170" spans="8:16">
+      <c r="Q169" s="18"/>
+      <c r="R169" s="18"/>
+    </row>
+    <row r="170" spans="8:18">
       <c r="H170" s="5" t="n">
         <v>56</v>
       </c>
@@ -6178,8 +6634,14 @@
       <c r="P170" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="171" spans="8:16">
+      <c r="Q170" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="R170" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="171" spans="8:18">
       <c r="H171" s="5" t="n">
         <v>58</v>
       </c>
@@ -6204,8 +6666,14 @@
       <c r="P171" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="172" spans="8:14">
+      <c r="Q171" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="R171" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="172" spans="8:18">
       <c r="H172" s="5" t="n">
         <v>44</v>
       </c>
@@ -6227,8 +6695,10 @@
       <c r="N172" s="5" t="n">
         <v>39</v>
       </c>
-    </row>
-    <row r="173" spans="9:14">
+      <c r="Q172" s="18"/>
+      <c r="R172" s="18"/>
+    </row>
+    <row r="173" spans="9:18">
       <c r="I173" s="6" t="s">
         <v>190</v>
       </c>
@@ -6241,6 +6711,8 @@
       <c r="N173" s="5" t="n">
         <v>40</v>
       </c>
+      <c r="Q173" s="18"/>
+      <c r="R173" s="18"/>
     </row>
     <row r="175" spans="10:10">
       <c r="J175"/>
@@ -6249,7 +6721,7 @@
       <c r="H176" s="4"/>
       <c r="I176" s="11"/>
       <c r="J176" s="12" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="K176" s="4"/>
       <c r="L176" s="4"/>
@@ -6261,12 +6733,12 @@
     <row r="177" spans="9:10">
       <c r="I177" s="8"/>
       <c r="J177" s="12" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
     </row>
     <row r="179" spans="9:9">
       <c r="I179" s="13" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
     </row>
     <row r="180" spans="8:16">
@@ -7329,7 +7801,7 @@
     </row>
     <row r="224" spans="9:9">
       <c r="I224" s="13" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
     </row>
     <row r="225" spans="8:16">
@@ -8391,7 +8863,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1740840553" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785693389" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -8400,10 +8872,10 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1740840553" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1740840553" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1740840553" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1740840553" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1785693389" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785693389" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785693389" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785693389" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
@@ -8412,7 +8884,7 @@
   </rowBreaks>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1740840553" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785693389" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
